--- a/www/download/COUNTRY.TUR.zdW16.xlsx
+++ b/www/download/COUNTRY.TUR.zdW16.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>Turquia</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Zero depreciation</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -847,1848 +852,3409 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.063</t>
+          <t>0.592708544595049</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>1.1251938050177</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.052</t>
+          <t>1.50114394366655</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.063</t>
+          <t>1.48874057991082</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.082</t>
+          <t>1.43232155573179</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.095</t>
+          <t>1.34334078035432</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.107</t>
+          <t>1.42412209225289</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.122</t>
+          <t>1.29760909518401</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.154</t>
+          <t>1.28747702768801</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0.141</t>
+          <t>1.54661988642095</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>0.151</t>
+          <t>1.50167015578968</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>1.66679693930306</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>1.79577658525242</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>0.178</t>
+          <t>1.89826060384692</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2.18687748753086</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>22.742</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>22.735</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>21.819</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>21.461</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>22.014</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>22.154</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>21.265</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>20.927</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>21.405</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>21.593</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>22.863</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>24.299</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>26.486</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>28.879</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>32.329</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>12.053</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>11.703</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>11.718</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>11.699</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>11.965</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>12.602</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>12.595</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>12.675</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>13.089</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>12.962</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>13.756</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>14.621</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>16.017</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>17.707</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>20.049</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>44566.468</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>44561.229</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>42519.449</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>41699.231</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>42223.767</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>42900.567</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>41391.622</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>39982.934</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>40627.392</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>40617.937</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>43006.312</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>45707.039</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>49822.229</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>54323.515</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>60812.638</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>23619.242</t>
+          <t>58665153130.6895</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>22938.392</t>
+          <t>56558187039.7788</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>22836.392</t>
+          <t>53467681131.3394</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>22730.842</t>
+          <t>54093924947.5943</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>22948.406</t>
+          <t>56299565088.2715</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>24402.524</t>
+          <t>55377981324.4553</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>24476.351</t>
+          <t>53868676937.166</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>24210.686</t>
+          <t>52988121265.2738</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>24855.65</t>
+          <t>51948633489.3483</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>24383.023</t>
+          <t>48071347740.5294</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>25875.796</t>
+          <t>54136007772.7666</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>27502.09</t>
+          <t>58221957750.9745</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>30129.227</t>
+          <t>59568918251.5574</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>33306.843</t>
+          <t>63540960204.7121</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>37712.431</t>
+          <t>70110755090.1184</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>7984518158.11916</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>7765255869.06021</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>6973313085.01473</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>7090114467.33463</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>7589809077.50995</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>7278954118.86172</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>6947731965.77505</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>6867803138.71299</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>6827047101.6151</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>6265487810.64662</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>7070802327.98043</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>7757031440.18528</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>8018309620.392</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>8340668009.79253</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>9079629787.32877</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>4053090.03163671</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>5519159.17803186</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>4693232.48822666</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>3607315.94492804</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>3036554.82007849</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>2499722.97833271</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>2285835.4354376</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>1867481.74189518</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>1644268.80261919</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>1853076.90019427</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>1701831.41578422</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>1703674.69814744</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>1772426.03519872</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>1849598.38513314</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>2082930.5465791</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>280384.654912469</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>276323.856550368</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>258843.529136753</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>272125.596363674</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>304635.876844534</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>324456.014866807</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>328363.878084003</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>346413.742660406</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>384860.071058913</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>344545.637602444</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>409842.893727465</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>467441.747108257</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>493956.497134742</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>527715.586224294</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>593164.621506673</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>532171.537835441</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>505545.959123278</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>481436.895902751</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>530279.588865923</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>608206.533595307</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>646160.544102737</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>664195.918956424</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>732894.587713629</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>783659.275714285</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>662729.10199628</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>824574.907116127</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>945537.388631886</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>944982.874141834</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>1002149.41579391</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>1109626.56681122</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>1.95812991244593</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1.95397761346094</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>2.27482671745718</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>2.20599083480597</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>2.02358145845862</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>2.35247668848008</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>2.52292677964147</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>2.52524461039474</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>2.64076146393069</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>2.89164000264548</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>2.65952756133556</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>2.54544005810335</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>2.75755345283449</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>2.99330640674049</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>3.15352078039902</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>0.592708544595049</t>
+          <t>662.475367921626</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.1251938050177</t>
+          <t>663.530122767417</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.50114394366655</t>
+          <t>595.07153764981</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>1.48874057991082</t>
+          <t>606.053087626906</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>1.43232155573179</t>
+          <t>634.3472204412</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>1.34334078035432</t>
+          <t>577.625960499604</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>1.42412209225289</t>
+          <t>551.607234604404</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>1.29760909518401</t>
+          <t>541.829962344814</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>1.28747702768801</t>
+          <t>521.605018193407</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>1.54661988642095</t>
+          <t>483.355192091661</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1.50167015578968</t>
+          <t>514.012770058194</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>1.66679693930306</t>
+          <t>530.553081404192</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>1.79577658525242</t>
+          <t>500.603543009443</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>1.89826060384692</t>
+          <t>471.049334218459</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>2.18687748753086</t>
+          <t>452.879497684722</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.077</t>
+          <t>974555427.0085</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.057</t>
+          <t>307313089.024134</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.055</t>
+          <t>1348878065.43308</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>3050454053.76141</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>3923164704.96993</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.112</t>
+          <t>4059186832.32932</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.122</t>
+          <t>4478482873.8643</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.151</t>
+          <t>6229103721.98669</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.173</t>
+          <t>6283303552.37433</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.145</t>
+          <t>5126698315.35229</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>0.171</t>
+          <t>5103098031.96002</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>0.182</t>
+          <t>5400775401.67356</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>0.187</t>
+          <t>4830512078.13521</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>0.195</t>
+          <t>4693743358.43929</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>0.191</t>
+          <t>4249108141.23972</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.111</t>
+          <t>1321501398.39545</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>-749774882.722251</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.082</t>
+          <t>147903776.27577</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0.104</t>
+          <t>1864835291.32614</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0.133</t>
+          <t>2447798577.99529</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>0.167</t>
+          <t>2784422104.75111</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>0.177</t>
+          <t>3409092138.25609</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>0.217</t>
+          <t>5097200901.85074</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>0.247</t>
+          <t>5134819206.67774</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>0.209</t>
+          <t>4004365063.3745</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>0.248</t>
+          <t>4332361987.49929</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>0.263</t>
+          <t>4878333501.65941</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>0.269</t>
+          <t>4393398084.03515</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>0.277</t>
+          <t>4334120985.935</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>0.269</t>
+          <t>3906698683.8113</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0.614</t>
+          <t>-346945971.386946</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.517</t>
+          <t>1057087971.74638</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.521</t>
+          <t>1200974289.15731</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>1185618762.43527</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0.791</t>
+          <t>1475366126.97464</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>0.903</t>
+          <t>1274764727.57821</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>1.028</t>
+          <t>1069390735.60821</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1131902820.13595</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>1.532</t>
+          <t>1148484345.69658</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>1.372</t>
+          <t>1122333251.97779</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1.466</t>
+          <t>770736044.460733</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>1.619</t>
+          <t>522441900.014145</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>1.645</t>
+          <t>437113994.100065</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>1.736</t>
+          <t>359622372.504291</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>1.761</t>
+          <t>342409457.428428</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.573</t>
+          <t>1959.68820210759</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.433</t>
+          <t>1960.05312851194</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.453</t>
+          <t>1948.75617029393</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0.584</t>
+          <t>1943.00064433772</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0.739</t>
+          <t>1918.00049395077</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>0.909</t>
+          <t>1936.47756723584</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>1.001</t>
+          <t>1943.27189863183</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1910.08315450644</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>1.394</t>
+          <t>1899.03944963143</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>1.151</t>
+          <t>1881.0444010303</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1881.0438989064</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>1.455</t>
+          <t>1881.04414776059</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>1.472</t>
+          <t>1881.04457153631</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>1.531</t>
+          <t>1881.04432422541</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>1.494</t>
+          <t>1881.04440465016</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.263</t>
+          <t>1959.68990387905</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.201</t>
+          <t>1960.05352036285</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.211</t>
+          <t>1948.75732887003</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.272</t>
+          <t>1943.00240280686</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.346</t>
+          <t>1918.00054324461</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.426</t>
+          <t>1936.47834685582</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0.469</t>
+          <t>1946.48693081301</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>0.581</t>
+          <t>1910.59052451573</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>0.664</t>
+          <t>1898.02887341059</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>0.559</t>
+          <t>1881.04395390098</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>0.653</t>
+          <t>1881.04321435871</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>1881.04345924987</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>0.703</t>
+          <t>1881.04465168247</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>0.731</t>
+          <t>1881.04358653187</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>0.711</t>
+          <t>1881.04415651156</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>68697.2882177323</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>72022.7306021434</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>72919.8160838307</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>84858.5570176292</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>109463.206216035</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>124456.673908114</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>141618.146008846</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>166152.091460797</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>199693.265287705</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>164727.421608497</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>176222.767020018</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>211351.996060945</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>226692.593014886</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>239787.47914582</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>249783.17694541</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>6964716378.90182</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>9588423880.96149</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>8630417159.09812</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>7977948889.59435</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>8323461718.39588</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>8069676370.64922</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>8537994947.24896</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>8144970009.63647</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>8575520570.35378</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>8492160033.34071</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>8585971715.35692</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>10529510306.0268</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>11578387477.2856</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>13179979456.9636</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>15767744745.7616</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>60334.161289277</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>44405.2832310506</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>49284.8859605759</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>66333.9022309332</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>92960.0576965628</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>111328.569872405</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>133621.710637518</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>161708.879312996</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>189044.44433106</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>134361.203370611</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>177495.72311436</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>232548.395412264</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>220047.876629648</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>240638.319112299</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>230133.810916991</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>44566.468</t>
+          <t>6795573304.68609</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>44561.229</t>
+          <t>5964921526.18567</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>42519.449</t>
+          <t>6594098749.30029</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>41699.231</t>
+          <t>8527393620.52399</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>42223.767</t>
+          <t>10216345753.7556</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>42900.567</t>
+          <t>10664040273.583</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>41391.622</t>
+          <t>12206728064.0695</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>39982.934</t>
+          <t>13988263230.2977</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>40627.392</t>
+          <t>14051549777.7546</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>40617.937</t>
+          <t>11033122910.1579</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>43006.312</t>
+          <t>13785696666.9443</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>45707.039</t>
+          <t>17453475383.5304</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>49822.229</t>
+          <t>15928224150.2534</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>54323.515</t>
+          <t>17935885826.3681</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>60812.638</t>
+          <t>18595043047.8048</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>23619.242</t>
+          <t>8363.12692845526</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>22938.392</t>
+          <t>27617.4473710929</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>22836.392</t>
+          <t>23634.9301232548</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>22730.842</t>
+          <t>18524.654786696</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>22948.406</t>
+          <t>16503.1485194727</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>24402.524</t>
+          <t>13128.1040357093</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>24476.351</t>
+          <t>7996.43537132829</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>24210.686</t>
+          <t>4443.21214780118</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>24855.65</t>
+          <t>10648.8209566445</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>24383.023</t>
+          <t>30366.2182378859</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>25875.796</t>
+          <t>-1272.95609434139</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>27502.09</t>
+          <t>-21196.3993513188</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>30129.227</t>
+          <t>6644.71638523777</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>33306.843</t>
+          <t>-850.839966478861</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>37712.431</t>
+          <t>19649.3660284189</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>66861.202</t>
+          <t>169143074.215725</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>63617.06</t>
+          <t>3623502354.77582</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>59901.262</t>
+          <t>2036318409.79783</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>60758.672</t>
+          <t>-549444730.929646</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>63665.363</t>
+          <t>-1892884035.35975</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>63541.612</t>
+          <t>-2594363902.9338</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>62525.036</t>
+          <t>-3668733116.82051</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>61665.672</t>
+          <t>-5843293220.66128</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>61703.958</t>
+          <t>-5476029207.40077</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>58349.147</t>
+          <t>-2540962876.81719</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>64166.555</t>
+          <t>-5199724951.5874</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>68936.069</t>
+          <t>-6923965077.50362</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>70302.258</t>
+          <t>-4349836672.96779</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>74866.841</t>
+          <t>-4755906369.40452</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>70110.755</t>
+          <t>-2827298302.04326</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.543</t>
+          <t>141572.019861457</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.512</t>
+          <t>104075.921680718</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.485</t>
+          <t>115397.100902023</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.535</t>
+          <t>149185.768112634</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>187086.293980193</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.665</t>
+          <t>231564.966646531</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.691</t>
+          <t>251352.597564173</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.769</t>
+          <t>304365.203833517</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.836</t>
+          <t>344407.533703592</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.719</t>
+          <t>281113.44094209</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>0.876</t>
+          <t>338852.994077071</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>0.999</t>
+          <t>365246.121918636</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>0.993</t>
+          <t>369364.442670364</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>1.057</t>
+          <t>379985.325610805</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>372074.857765008</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>30908.847</t>
+          <t>0.248578095399754</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>30913.859</t>
+          <t>0.233964750980243</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>28746.786</t>
+          <t>0.247912083147165</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>27759.585</t>
+          <t>0.266106916313458</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>28199.084</t>
+          <t>0.268971019958362</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>27806.896</t>
+          <t>0.28668728286791</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>26631.491</t>
+          <t>0.284710501397768</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>25045.639</t>
+          <t>0.303576577937043</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>25512.305</t>
+          <t>0.272084859097244</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>24991.77</t>
+          <t>0.254984505503539</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>26907.511</t>
+          <t>0.276003571941441</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>28782.969</t>
+          <t>0.263889314402306</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>31137.553</t>
+          <t>0.264183669082549</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>33459.636</t>
+          <t>0.261636835122901</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>37478.572</t>
+          <t>0.250671156558733</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.251</t>
+          <t>76869.9673612266</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.249</t>
+          <t>56617.4271590379</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.233</t>
+          <t>55005.4093037703</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.245</t>
+          <t>70453.9352684165</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.275</t>
+          <t>90151.4940138017</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.291</t>
+          <t>112258.716071965</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.294</t>
+          <t>121919.295275989</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.312</t>
+          <t>151035.944678674</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.345</t>
+          <t>172520.277448417</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.308</t>
+          <t>145363.508301631</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>0.367</t>
+          <t>171310.339762505</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>0.417</t>
+          <t>182130.472843148</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>187248.073575527</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>0.472</t>
+          <t>194768.50673348</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>0.593</t>
+          <t>191058.954525972</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>8747.095</t>
+          <t>110517.227671272</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>8408.936</t>
+          <t>80011.2426880812</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>7531.582</t>
+          <t>81916.1168548035</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>7698.138</t>
+          <t>104194.11031238</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>8283.161</t>
+          <t>132875.966183165</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>8050.893</t>
+          <t>166834.054112298</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>7760.331</t>
+          <t>176569.718392115</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>7698.165</t>
+          <t>216989.67000379</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>7757.295</t>
+          <t>246902.969237804</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>7211.382</t>
+          <t>209210.39196354</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>8012.093</t>
+          <t>248306.483912359</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>8769.952</t>
+          <t>263069.481937508</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>9047.748</t>
+          <t>268810.687767447</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>9399.615</t>
+          <t>277019.472668986</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>9079.63</t>
+          <t>269473.128882797</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>170.02</t>
+          <t>614374.722303938</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>172.79</t>
+          <t>516854.10752241</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>203.21</t>
+          <t>521436.964823224</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>195.28</t>
+          <t>630339.094475198</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>177.05</t>
+          <t>790552.603058632</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>203.1</t>
+          <t>902575.944559943</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>215.4</t>
+          <t>1028360.06758582</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>214.5</t>
+          <t>1200274.59613604</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>220.42</t>
+          <t>1532112.16039502</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>238.12</t>
+          <t>1371525.38480416</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>222.96</t>
+          <t>1466155.97759113</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>213.59</t>
+          <t>1618664.68648815</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>1644655.7948755</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>254.34</t>
+          <t>1736114.02768674</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>315.35</t>
+          <t>1761056.4551636</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>compensation.emp.s.cu</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>4.683</t>
+          <t>477291.918085935</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>6.246</t>
+          <t>446779.133525425</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>5.32</t>
+          <t>444520.775629166</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>4.111</t>
+          <t>448092.079695687</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>3.487</t>
+          <t>485984.793028937</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2.909</t>
+          <t>538399.580184543</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>2.684</t>
+          <t>559068.638776799</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>2.193</t>
+          <t>582361.772029494</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>1.967</t>
+          <t>599517.345601476</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>2.277</t>
+          <t>580255.584392214</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>2.044</t>
+          <t>629102.733933385</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>2.042</t>
+          <t>682537.189244607</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>2.113</t>
+          <t>702320.659425242</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>2.198</t>
+          <t>731170.240016365</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>2.083</t>
+          <t>752642.833540237</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>321269.836510189</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>303295.865749027</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>295986.999016533</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>301062.810219328</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>328424.902905874</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>361954.1336089</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>380330.341478819</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>401954.67494839</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>415006.747305344</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>396167.137794108</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>434027.334652572</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>471509.292852227</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>486048.375482644</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>506570.875620676</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>528423.78260891</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>152720.098332065</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>120925.642559596</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>129270.52417926</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>167737.592662612</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>212635.739975419</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>258757.045127827</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>292784.910459802</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>364375.254479745</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>416864.521282252</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>349717.722029839</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>404664.286838446</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>427148.314364583</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>434491.202268087</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>454231.379616431</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>441446.05838108</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>23619242000</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>22938392000</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>22836392000</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>22730842000</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>22948406000</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>24402524000</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>24476351000</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>24210686000</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>24855650000</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>24383023000</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>25875796000</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>27502090000</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>30129227000</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>33306843000</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>37712431000</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>44566468240.5365</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>44561228769.3933</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>42519448969.283</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>41699231172.2026</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>42223767337.2428</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>42900567013.1925</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>41391622196.0747</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>39982933638.3123</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>40627391548.6242</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>40617937004.5503</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>43006311701.3585</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>45707038614.23</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>49822228973.3588</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>54323515491.3295</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>60812637696.3403</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>30908847141.3551</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>30913858730.9283</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>28746785708.734</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>27759585499.9764</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>28199084405.1726</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>27806896128.0379</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>26631491042.7846</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>25045639184.3616</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>25512305405.8168</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>24991769801.2339</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>26907510632.407</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>28782969323.4627</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>31137552862.3905</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>33459636392.7632</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>37478572296.7034</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>22741592</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>22734700</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>21818750</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>21461235</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>22014471</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>22153910</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>21264783</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>20927003</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>21405044</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>21593295</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>22863011</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>24298768</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>26486468</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>28879456</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>32329192</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>12052551</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>11702944</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>11718445</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>11698834</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>11964755</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>12601501</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>12595433</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>12675200</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>13088538</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>12962492</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>13756083</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>14620651</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>16017285</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>17706570</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>20048666</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>44566468240.5365</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>44561228769.3933</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>42519448969.283</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>41699231172.2026</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>42223767337.2428</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>42900567013.1925</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>41391622196.0747</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>39982933638.3123</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>40627391548.6242</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>40617937004.5503</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>43006311701.3585</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>45707038614.23</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>49822228973.3588</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>54323515491.3295</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>60812637696.3403</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>23619242000</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>22938392000</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>22836392000</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>22730842000</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>22948406000</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>24402524000</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>24476351000</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>24210686000</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>24855650000</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>24383023000</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>25875796000</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>27502090000</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>30129227000</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>33306843000</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>37712431000</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>573083.38040896</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>433009.817203656</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>453253.996969534</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>583875.87766493</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>738903.073891896</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>909018.021570824</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>1001427.87541185</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>1230394.04894565</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>1394028.2577365</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>1151168.91465528</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>1359962.68281551</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>1455482.26845111</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>1472372.21208569</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>1530674.10028907</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>1494427.53535721</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>263237.344562156</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>200936.879026552</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>211186.631041659</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>271931.722454549</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>345511.718027433</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>425591.111894991</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>469354.616212552</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>581364.938355215</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>663767.445470711</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>558928.097829074</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>652970.771416704</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>690217.811900883</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>703301.895047276</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>731250.830686698</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>710919.200524792</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>2564006.84819648</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>2681602.9965537</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>2692674.93818625</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>2664900.42294372</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>2847552.55768366</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>2891320.1535879</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>3226501.91310769</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>3199592.35742673</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>3624838.34191758</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>3748406.51145137</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>3714614.07002115</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>4143466.19609792</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>4246526.50770055</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>4507256.04632715</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>4812329.09351161</t>
         </is>
       </c>
     </row>
@@ -2699,7 +4265,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2722,36 +4288,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -2763,331 +4344,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3124,6 +5069,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Zero depreciation</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>zdW16</t>
